--- a/data/trans_dic/P22$concerIndv-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,63</t>
+          <t>0,41; 1,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,58</t>
+          <t>0,38; 1,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,26; 1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,26</t>
+          <t>1,01; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,51</t>
+          <t>1,15; 2,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,18</t>
+          <t>0,75; 2,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,01</t>
+          <t>0,49; 1,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,78</t>
+          <t>1,16; 2,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,85</t>
+          <t>0,93; 1,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,64</t>
+          <t>0,71; 1,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,5</t>
+          <t>0,49; 1,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,62</t>
+          <t>1,3; 2,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,46</t>
+          <t>1,15; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,76</t>
+          <t>2,14; 3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,22</t>
+          <t>1,74; 3,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,29</t>
+          <t>2,88; 5,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,05</t>
+          <t>2,93; 5,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,84</t>
+          <t>2,9; 5,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,32</t>
+          <t>2,63; 4,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,36</t>
+          <t>4,26; 7,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,49</t>
+          <t>2,2; 3,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,01</t>
+          <t>2,69; 4,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,48</t>
+          <t>2,4; 3,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 6,0</t>
+          <t>4,08; 5,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 12,55</t>
+          <t>7,44; 12,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,17</t>
+          <t>7,2; 13,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 13,46</t>
+          <t>8,28; 13,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,09</t>
+          <t>13,32; 18,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 13,28</t>
+          <t>7,71; 13,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,61</t>
+          <t>5,57; 10,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,32; 17,8</t>
+          <t>11,24; 17,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 22,64</t>
+          <t>17,34; 22,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,92</t>
+          <t>8,33; 11,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,01</t>
+          <t>6,82; 10,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,64; 14,68</t>
+          <t>10,56; 14,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,99; 19,95</t>
+          <t>16,04; 20,01</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,4</t>
+          <t>2,27; 3,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 3,98</t>
+          <t>2,71; 4,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>2,71; 4,01</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4,66; 6,97</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,28; 4,7</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>2,78; 4,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,64; 7,07</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3,28; 4,66</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 3,98</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,23</t>
+          <t>3,73; 5,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 8,69</t>
+          <t>6,37; 8,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,82</t>
+          <t>2,97; 3,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 3,83</t>
+          <t>2,85; 3,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,47</t>
+          <t>3,45; 4,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,64</t>
+          <t>5,91; 7,62</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3964; 16758</t>
+          <t>4242; 16484</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3630; 15363</t>
+          <t>3713; 15562</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1946; 12097</t>
+          <t>1954; 12045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5163; 16809</t>
+          <t>5215; 17201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13445; 32965</t>
+          <t>15066; 32735</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9424; 29143</t>
+          <t>9991; 28444</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4415; 19909</t>
+          <t>4841; 19497</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8598; 20911</t>
+          <t>8716; 21947</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20837; 43413</t>
+          <t>21816; 44692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16072; 37826</t>
+          <t>16351; 36590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8652; 26174</t>
+          <t>8607; 26166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16534; 33243</t>
+          <t>16531; 33501</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19838; 41589</t>
+          <t>19513; 42171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42010; 73822</t>
+          <t>41956; 74929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36549; 66677</t>
+          <t>35978; 66287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65960; 121210</t>
+          <t>65945; 122531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47903; 80188</t>
+          <t>46544; 80679</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>51738; 84995</t>
+          <t>50896; 88102</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51734; 85901</t>
+          <t>52155; 84693</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98273; 164606</t>
+          <t>95289; 162330</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>74761; 114180</t>
+          <t>72109; 112515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100856; 149263</t>
+          <t>100002; 151493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97429; 141430</t>
+          <t>97374; 140764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184925; 271473</t>
+          <t>184855; 270988</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40569; 69190</t>
+          <t>40998; 69723</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35100; 63388</t>
+          <t>34655; 64453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44033; 73484</t>
+          <t>45202; 74613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84270; 123452</t>
+          <t>86109; 122750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35529; 63286</t>
+          <t>36731; 64513</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24313; 48672</t>
+          <t>25567; 49187</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62181; 97774</t>
+          <t>61749; 97156</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113378; 149561</t>
+          <t>114510; 150524</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85178; 122519</t>
+          <t>85660; 122695</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66717; 103477</t>
+          <t>64117; 102813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116480; 160736</t>
+          <t>115663; 160756</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>208975; 260739</t>
+          <t>209592; 261495</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>75537; 111272</t>
+          <t>74314; 112315</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>91187; 136102</t>
+          <t>92531; 137951</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93681; 134968</t>
+          <t>91322; 135306</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160201; 244036</t>
+          <t>160950; 240599</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110874; 157521</t>
+          <t>110901; 158730</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96955; 141498</t>
+          <t>98826; 142128</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131597; 184328</t>
+          <t>131660; 182052</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>230968; 317372</t>
+          <t>232627; 316351</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193013; 253601</t>
+          <t>197272; 256187</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>204254; 267092</t>
+          <t>198515; 265599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>239171; 308421</t>
+          <t>237726; 304725</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>423177; 542803</t>
+          <t>420062; 540977</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerIndv-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,6</t>
+          <t>0,35; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,6</t>
+          <t>0,39; 1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,6</t>
+          <t>0,26; 1,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,34</t>
+          <t>0,89; 3,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,49</t>
+          <t>1,09; 2,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,13</t>
+          <t>0,73; 2,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,97</t>
+          <t>0,52; 2,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,91</t>
+          <t>1,08; 2,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,91</t>
+          <t>0,92; 1,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,58</t>
+          <t>0,69; 1,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,5</t>
+          <t>0,49; 1,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,64</t>
+          <t>1,22; 2,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,5</t>
+          <t>1,19; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,82</t>
+          <t>2,16; 3,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,2</t>
+          <t>1,69; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,35</t>
+          <t>3,81; 5,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,09</t>
+          <t>2,96; 4,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,01</t>
+          <t>2,9; 4,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,26</t>
+          <t>2,66; 4,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,25</t>
+          <t>6,12; 8,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,43</t>
+          <t>2,25; 3,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,07</t>
+          <t>2,71; 4,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,47</t>
+          <t>2,36; 3,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,98</t>
+          <t>5,21; 6,65</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 12,64</t>
+          <t>7,35; 12,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 13,39</t>
+          <t>7,39; 13,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,67</t>
+          <t>8,18; 13,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 18,98</t>
+          <t>13,52; 19,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,71; 13,54</t>
+          <t>7,67; 13,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,72</t>
+          <t>5,43; 10,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 17,69</t>
+          <t>11,74; 17,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,34; 22,79</t>
+          <t>17,37; 22,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,94</t>
+          <t>8,12; 12,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 10,94</t>
+          <t>6,72; 10,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,68</t>
+          <t>10,68; 14,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,04; 20,01</t>
+          <t>16,16; 19,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,29; 3,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,04</t>
+          <t>2,69; 4,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,01</t>
+          <t>2,72; 4,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,66; 6,97</t>
+          <t>5,75; 7,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,7</t>
+          <t>3,3; 4,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,0</t>
+          <t>2,77; 4,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,16</t>
+          <t>3,72; 5,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,66</t>
+          <t>7,62; 9,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 3,81</t>
+          <t>2,87; 3,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,42</t>
+          <t>3,43; 4,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,62</t>
+          <t>6,94; 8,1</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9778</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>24580</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4242; 16484</t>
+          <t>3574; 15721</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3713; 15562</t>
+          <t>3789; 15534</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1954; 12045</t>
+          <t>1982; 11266</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5215; 17201</t>
+          <t>5126; 17674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15066; 32735</t>
+          <t>14274; 32394</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9991; 28444</t>
+          <t>9795; 27612</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4841; 19497</t>
+          <t>5154; 20587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8716; 21947</t>
+          <t>8895; 21349</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21816; 44692</t>
+          <t>21513; 42613</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16351; 36590</t>
+          <t>16034; 37506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8607; 26166</t>
+          <t>8626; 26596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16531; 33501</t>
+          <t>17132; 34696</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95219</t>
+          <t>106188</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>135376</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>230595</t>
+          <t>259286</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19513; 42171</t>
+          <t>20179; 41544</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41956; 74929</t>
+          <t>42319; 77366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35978; 66287</t>
+          <t>34995; 63960</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65945; 122531</t>
+          <t>84964; 128837</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46544; 80679</t>
+          <t>47000; 78777</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50896; 88102</t>
+          <t>51036; 85675</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52155; 84693</t>
+          <t>52760; 84433</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>95289; 162330</t>
+          <t>132835; 175834</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72109; 112515</t>
+          <t>73801; 111921</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100002; 151493</t>
+          <t>100853; 148784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97374; 140764</t>
+          <t>95918; 139279</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184855; 270988</t>
+          <t>229106; 292837</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102361</t>
+          <t>115680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131709</t>
+          <t>146000</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>234070</t>
+          <t>261680</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40998; 69723</t>
+          <t>40544; 69024</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34655; 64453</t>
+          <t>35544; 66349</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45202; 74613</t>
+          <t>44633; 73998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86109; 122750</t>
+          <t>96223; 138994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36731; 64513</t>
+          <t>36564; 63137</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25567; 49187</t>
+          <t>24926; 48717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61749; 97156</t>
+          <t>64450; 95928</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>114510; 150524</t>
+          <t>127668; 166344</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>85660; 122695</t>
+          <t>83419; 123932</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64117; 102813</t>
+          <t>63168; 100675</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115663; 160756</t>
+          <t>116955; 161192</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>209592; 261495</t>
+          <t>233757; 289177</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>280760</t>
+          <t>313400</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>488118</t>
+          <t>545545</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74314; 112315</t>
+          <t>74994; 111322</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92531; 137951</t>
+          <t>91916; 138585</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91322; 135306</t>
+          <t>91625; 134786</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160950; 240599</t>
+          <t>202267; 270297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>110901; 158730</t>
+          <t>111302; 156032</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>98826; 142128</t>
+          <t>98284; 146292</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>131660; 182052</t>
+          <t>131027; 184847</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>232627; 316351</t>
+          <t>283837; 344564</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>197272; 256187</t>
+          <t>197741; 255619</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>198515; 265599</t>
+          <t>200313; 264821</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237726; 304725</t>
+          <t>236314; 300750</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>420062; 540977</t>
+          <t>502728; 586688</t>
         </is>
       </c>
     </row>
